--- a/export from sqliteonline.com.xlsx
+++ b/export from sqliteonline.com.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>ID</t>
   </si>
@@ -33,6 +33,12 @@
   </si>
   <si>
     <t>Full Convert is industry standard for database migration. Over 40 database formats supported with unparalleled speed, ease of use, and migration customization.</t>
+  </si>
+  <si>
+    <t>https://cmsnap.sqliteonline.com/</t>
+  </si>
+  <si>
+    <t>CMSnap – one self-hosted binary, 10k sites, 10k SQLite DBs, site-scoped MCP, 1M req/s.</t>
   </si>
   <si>
     <t>SQL Online IDE</t>
@@ -586,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -906,6 +912,17 @@
       </c>
       <c r="C29" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -921,10 +938,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
